--- a/event_registration_forms/012_emergency_plan_for_event_hosting--event_registration_forms.xlsx
+++ b/event_registration_forms/012_emergency_plan_for_event_hosting--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>event_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event Type</t>
+          <t>Event Type 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>event_status</t>
+          <t>event_status_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event Status</t>
+          <t>Event Status 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_date_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Date 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>additional_contacts</t>
+          <t>additional_contacts_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Additional Contacts</t>
+          <t>Additional Contacts 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>event_venue</t>
+          <t>event_venue_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Event Venue</t>
+          <t>Event Venue 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1078,7 +1078,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1171,7 +1171,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>event_type_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1188,7 +1188,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_type_choices</t>
+          <t>event_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_status_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1222,7 +1222,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_status_choices</t>
+          <t>event_status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>additional_contacts_choices</t>
+          <t>additional_contacts_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>additional_contacts_choices</t>
+          <t>additional_contacts_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
